--- a/docs/UNIVERSAL_TAG_MASTER_BUILD.xlsx
+++ b/docs/UNIVERSAL_TAG_MASTER_BUILD.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>(add ASS_TAG_1_TXT directly — not a calc value)</t>
+          <t>(add ASS_DISPLAY_TXT directly - not a calc value)</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>ASS_TAG_1_TXT</t>
+          <t>ASS_DISPLAY_TXT</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
@@ -3634,7 +3634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5666,6 +5666,33 @@
       <c r="E75" s="38" t="inlineStr">
         <is>
           <t>badge master on/off</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ASS_DISPLAY_TXT</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>STINGTags_ISO19650</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>6954e197-0524-5620-a2bb-aea7f274475a</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>T1 on-drawing tag (display-mode + mask resolved)</t>
         </is>
       </c>
     </row>

--- a/docs/UNIVERSAL_TAG_MASTER_BUILD.xlsx
+++ b/docs/UNIVERSAL_TAG_MASTER_BUILD.xlsx
@@ -1619,7 +1619,7 @@
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>if(TAG_PARA_STATE_5_BOOL, ASS_CST_STALE_BOOL, "")</t>
+          <t>if(TAG_PARA_STATE_5_BOOL, ASS_CST_STALE_TXT, "")</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>ASS_CST_STALE_BOOL</t>
+          <t>ASS_CST_STALE_TXT</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr"/>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="C51" s="28" t="inlineStr">
         <is>
-          <t>Show T8 - Coordination - ASS_CRITICALITY_RATING_NR</t>
+          <t>Show T8 - Coordination - ASS_CRITICALITY_RATING_TXT</t>
         </is>
       </c>
       <c r="D51" s="29" t="inlineStr">
         <is>
-          <t>if(TAG_PARA_STATE_8_BOOL, ASS_CRITICALITY_RATING_NR, "")</t>
+          <t>if(TAG_PARA_STATE_8_BOOL, ASS_CRITICALITY_RATING_TXT, "")</t>
         </is>
       </c>
       <c r="E51" s="26" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="J51" s="26" t="inlineStr">
         <is>
-          <t>ASS_CRITICALITY_RATING_NR</t>
+          <t>ASS_CRITICALITY_RATING_TXT</t>
         </is>
       </c>
       <c r="K51" s="26" t="inlineStr"/>
@@ -3809,7 +3809,7 @@
     <row r="7">
       <c r="A7" s="38" t="inlineStr">
         <is>
-          <t>ASS_CRITICALITY_RATING_NR</t>
+          <t>ASS_CRITICALITY_RATING_TXT</t>
         </is>
       </c>
       <c r="B7" s="38" t="inlineStr">
@@ -3971,7 +3971,7 @@
     <row r="13">
       <c r="A13" s="38" t="inlineStr">
         <is>
-          <t>ASS_CST_STALE_BOOL</t>
+          <t>ASS_CST_STALE_TXT</t>
         </is>
       </c>
       <c r="B13" s="38" t="inlineStr">
